--- a/form/01_사용인감계(범용).xlsx
+++ b/form/01_사용인감계(범용).xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_1M\Desktop\업무용파일_이서하\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_1M\Desktop\seohabucks\form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F3B933-E41A-4C80-8B99-4279AD9A7C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFA01C4-8C45-4DB8-B138-56026B1EA4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제출처 : 주식회사 백마종합건설</t>
+    <t>제출처 : 한국수자원공사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2233,11 +2233,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:AF3"/>
-    <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="Q28:T28"/>
-    <mergeCell ref="J5:M11"/>
-    <mergeCell ref="N5:V11"/>
     <mergeCell ref="A34:V35"/>
     <mergeCell ref="X27:AE28"/>
     <mergeCell ref="X29:AE33"/>
@@ -2245,6 +2240,11 @@
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="S24:T24"/>
     <mergeCell ref="J31:O31"/>
+    <mergeCell ref="A1:AF3"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="J5:M11"/>
+    <mergeCell ref="N5:V11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/form/01_사용인감계(범용).xlsx
+++ b/form/01_사용인감계(범용).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_1M\Desktop\seohabucks\form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFA01C4-8C45-4DB8-B138-56026B1EA4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C67092-71DB-4B10-946F-E1C5A33F2085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제출처 : 한국수자원공사</t>
+    <t>제출처 : K-water 특정공법·자재 심사위원회 제출</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2233,6 +2233,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:AF3"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="J5:M11"/>
+    <mergeCell ref="N5:V11"/>
     <mergeCell ref="A34:V35"/>
     <mergeCell ref="X27:AE28"/>
     <mergeCell ref="X29:AE33"/>
@@ -2240,11 +2245,6 @@
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="S24:T24"/>
     <mergeCell ref="J31:O31"/>
-    <mergeCell ref="A1:AF3"/>
-    <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="Q28:T28"/>
-    <mergeCell ref="J5:M11"/>
-    <mergeCell ref="N5:V11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2733,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="P24" s="45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="45"/>
       <c r="R24" s="8" t="s">

--- a/form/01_사용인감계(범용).xlsx
+++ b/form/01_사용인감계(범용).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_1M\Desktop\seohabucks\form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C67092-71DB-4B10-946F-E1C5A33F2085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED06449-3496-42DE-9003-3C51AFA5BA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2233,11 +2233,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:AF3"/>
-    <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="Q28:T28"/>
-    <mergeCell ref="J5:M11"/>
-    <mergeCell ref="N5:V11"/>
     <mergeCell ref="A34:V35"/>
     <mergeCell ref="X27:AE28"/>
     <mergeCell ref="X29:AE33"/>
@@ -2245,6 +2240,11 @@
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="S24:T24"/>
     <mergeCell ref="J31:O31"/>
+    <mergeCell ref="A1:AF3"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="J5:M11"/>
+    <mergeCell ref="N5:V11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2739,7 +2739,9 @@
       <c r="R24" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="S24" s="45"/>
+      <c r="S24" s="45">
+        <v>12</v>
+      </c>
       <c r="T24" s="45"/>
       <c r="U24" s="8" t="s">
         <v>3</v>

--- a/form/01_사용인감계(범용).xlsx
+++ b/form/01_사용인감계(범용).xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_1M\Desktop\seohabucks\form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED06449-3496-42DE-9003-3C51AFA5BA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B82F685-7963-41E4-8D97-3AEB932C4C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용인감계 (흥화)" sheetId="4" r:id="rId1"/>
     <sheet name="사용인감계 (쌍용건설)" sheetId="3" r:id="rId2"/>
-    <sheet name="사용인감계 (선영건설)" sheetId="5" r:id="rId3"/>
+    <sheet name="사용인감계 (범용)" sheetId="5" r:id="rId3"/>
+    <sheet name="사용인감계 (심의갈때)" sheetId="6" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'사용인감계 (범용)'!$A$1:$AF$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'사용인감계 (심의갈때)'!$A$1:$AF$35</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="28">
   <si>
     <t>사 용 인 감 계</t>
   </si>
@@ -112,7 +117,38 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제출처 : K-water 특정공법·자재 심사위원회 제출</t>
+    <t xml:space="preserve"> K-water 특정공법·자재 심사위원회 제출</t>
+  </si>
+  <si>
+    <t>제출처 : IPARK현대산업개발㈜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> K-water 특정공법·자재 심사위원회 제출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>붙임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제출처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코오롱글로벌㈜ - 현장설명회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">법인인감증명서 1부. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">   위 인감은 "㈜대호스토퍼"에서 사용하는 사용 인감임을 확인합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -120,7 +156,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="돋움"/>
@@ -175,6 +211,12 @@
     <font>
       <u/>
       <sz val="15"/>
+      <name val="궁서체"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <name val="궁서체"/>
       <family val="1"/>
       <charset val="129"/>
@@ -377,7 +419,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -429,6 +471,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -516,6 +561,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
@@ -527,6 +578,51 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -845,108 +941,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="24"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="27"/>
     </row>
     <row r="3" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="26"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="26"/>
+      <c r="AB3" s="26"/>
+      <c r="AC3" s="26"/>
+      <c r="AD3" s="26"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="27"/>
     </row>
     <row r="4" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
@@ -954,72 +1050,72 @@
     </row>
     <row r="5" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="38"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="39"/>
       <c r="AF5" s="3"/>
     </row>
     <row r="6" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="41"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="42"/>
       <c r="AF6" s="3"/>
     </row>
     <row r="7" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="42"/>
       <c r="AF7" s="3"/>
     </row>
     <row r="8" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="41"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="42"/>
       <c r="AF8" s="3"/>
     </row>
     <row r="9" spans="1:32" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1032,19 +1128,19 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="41"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="42"/>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
@@ -1066,19 +1162,19 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="41"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="42"/>
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
@@ -1100,19 +1196,19 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="44"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="45"/>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
@@ -1301,22 +1397,22 @@
     </row>
     <row r="24" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
-      <c r="M24" s="45">
+      <c r="M24" s="46">
         <v>2026</v>
       </c>
-      <c r="N24" s="45"/>
+      <c r="N24" s="46"/>
       <c r="O24" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="P24" s="45">
+      <c r="P24" s="46">
         <v>1</v>
       </c>
-      <c r="Q24" s="45"/>
+      <c r="Q24" s="46"/>
       <c r="R24" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="S24" s="45"/>
-      <c r="T24" s="45"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
       <c r="U24" s="8" t="s">
         <v>3</v>
       </c>
@@ -1338,22 +1434,22 @@
       <c r="J27" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
       <c r="U27" s="5"/>
       <c r="W27" s="5"/>
-      <c r="X27" s="47" t="s">
+      <c r="X27" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="47"/>
-      <c r="AC27" s="47"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="47"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="50"/>
+      <c r="AA27" s="50"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="50"/>
+      <c r="AE27" s="50"/>
       <c r="AF27" s="9"/>
     </row>
     <row r="28" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1364,20 +1460,20 @@
       <c r="J28" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
       <c r="U28" s="5"/>
       <c r="W28" s="5"/>
-      <c r="X28" s="47"/>
-      <c r="Y28" s="47"/>
-      <c r="Z28" s="47"/>
-      <c r="AA28" s="47"/>
-      <c r="AB28" s="47"/>
-      <c r="AC28" s="47"/>
-      <c r="AD28" s="47"/>
-      <c r="AE28" s="47"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
+      <c r="AA28" s="50"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="50"/>
+      <c r="AE28" s="50"/>
       <c r="AF28" s="9"/>
     </row>
     <row r="29" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1388,14 +1484,14 @@
       <c r="J29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="48"/>
-      <c r="AE29" s="48"/>
+      <c r="X29" s="51"/>
+      <c r="Y29" s="51"/>
+      <c r="Z29" s="51"/>
+      <c r="AA29" s="51"/>
+      <c r="AB29" s="51"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="51"/>
+      <c r="AE29" s="51"/>
       <c r="AF29" s="3"/>
     </row>
     <row r="30" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1403,14 +1499,14 @@
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="48"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="48"/>
-      <c r="AE30" s="48"/>
+      <c r="X30" s="51"/>
+      <c r="Y30" s="51"/>
+      <c r="Z30" s="51"/>
+      <c r="AA30" s="51"/>
+      <c r="AB30" s="51"/>
+      <c r="AC30" s="51"/>
+      <c r="AD30" s="51"/>
+      <c r="AE30" s="51"/>
       <c r="AF30" s="3"/>
     </row>
     <row r="31" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -1418,96 +1514,96 @@
       <c r="C31" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J31" s="49" t="s">
+      <c r="J31" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="49"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="48"/>
-      <c r="AB31" s="48"/>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="48"/>
-      <c r="AE31" s="48"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
+      <c r="X31" s="51"/>
+      <c r="Y31" s="51"/>
+      <c r="Z31" s="51"/>
+      <c r="AA31" s="51"/>
+      <c r="AB31" s="51"/>
+      <c r="AC31" s="51"/>
+      <c r="AD31" s="51"/>
+      <c r="AE31" s="51"/>
       <c r="AF31" s="3"/>
     </row>
     <row r="32" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="48"/>
-      <c r="AA32" s="48"/>
-      <c r="AB32" s="48"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="48"/>
-      <c r="AE32" s="48"/>
+      <c r="X32" s="51"/>
+      <c r="Y32" s="51"/>
+      <c r="Z32" s="51"/>
+      <c r="AA32" s="51"/>
+      <c r="AB32" s="51"/>
+      <c r="AC32" s="51"/>
+      <c r="AD32" s="51"/>
+      <c r="AE32" s="51"/>
       <c r="AF32" s="3"/>
     </row>
     <row r="33" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="48"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="48"/>
-      <c r="AE33" s="48"/>
+      <c r="X33" s="51"/>
+      <c r="Y33" s="51"/>
+      <c r="Z33" s="51"/>
+      <c r="AA33" s="51"/>
+      <c r="AB33" s="51"/>
+      <c r="AC33" s="51"/>
+      <c r="AD33" s="51"/>
+      <c r="AE33" s="51"/>
       <c r="AF33" s="3"/>
     </row>
     <row r="34" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="17"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
       <c r="AF34" s="3"/>
     </row>
     <row r="35" spans="1:32" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
+      <c r="V35" s="21"/>
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35" s="15"/>
@@ -1557,108 +1653,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="24"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="26"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="27"/>
     </row>
     <row r="3" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="26"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="26"/>
+      <c r="AB3" s="26"/>
+      <c r="AC3" s="26"/>
+      <c r="AD3" s="26"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="27"/>
     </row>
     <row r="4" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
@@ -1666,72 +1762,72 @@
     </row>
     <row r="5" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="38"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="39"/>
       <c r="AF5" s="3"/>
     </row>
     <row r="6" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="41"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="42"/>
       <c r="AF6" s="3"/>
     </row>
     <row r="7" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="42"/>
       <c r="AF7" s="3"/>
     </row>
     <row r="8" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="41"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="42"/>
       <c r="AF8" s="3"/>
     </row>
     <row r="9" spans="1:32" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1744,19 +1840,19 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="41"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="42"/>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
@@ -1778,19 +1874,19 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="41"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="42"/>
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
@@ -1812,19 +1908,19 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="44"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="45"/>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
@@ -2013,22 +2109,22 @@
     </row>
     <row r="24" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
-      <c r="M24" s="45">
+      <c r="M24" s="46">
         <v>2026</v>
       </c>
-      <c r="N24" s="45"/>
+      <c r="N24" s="46"/>
       <c r="O24" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="P24" s="45">
+      <c r="P24" s="46">
         <v>1</v>
       </c>
-      <c r="Q24" s="45"/>
+      <c r="Q24" s="46"/>
       <c r="R24" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="S24" s="45"/>
-      <c r="T24" s="45"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
       <c r="U24" s="8" t="s">
         <v>3</v>
       </c>
@@ -2050,22 +2146,22 @@
       <c r="J27" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
       <c r="U27" s="5"/>
       <c r="W27" s="5"/>
-      <c r="X27" s="47" t="s">
+      <c r="X27" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="47"/>
-      <c r="AC27" s="47"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="47"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="50"/>
+      <c r="AA27" s="50"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="50"/>
+      <c r="AE27" s="50"/>
       <c r="AF27" s="9"/>
     </row>
     <row r="28" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2076,20 +2172,20 @@
       <c r="J28" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
       <c r="U28" s="5"/>
       <c r="W28" s="5"/>
-      <c r="X28" s="47"/>
-      <c r="Y28" s="47"/>
-      <c r="Z28" s="47"/>
-      <c r="AA28" s="47"/>
-      <c r="AB28" s="47"/>
-      <c r="AC28" s="47"/>
-      <c r="AD28" s="47"/>
-      <c r="AE28" s="47"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
+      <c r="AA28" s="50"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="50"/>
+      <c r="AE28" s="50"/>
       <c r="AF28" s="9"/>
     </row>
     <row r="29" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2100,14 +2196,14 @@
       <c r="J29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="48"/>
-      <c r="AE29" s="48"/>
+      <c r="X29" s="51"/>
+      <c r="Y29" s="51"/>
+      <c r="Z29" s="51"/>
+      <c r="AA29" s="51"/>
+      <c r="AB29" s="51"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="51"/>
+      <c r="AE29" s="51"/>
       <c r="AF29" s="3"/>
     </row>
     <row r="30" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2115,14 +2211,14 @@
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="48"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="48"/>
-      <c r="AE30" s="48"/>
+      <c r="X30" s="51"/>
+      <c r="Y30" s="51"/>
+      <c r="Z30" s="51"/>
+      <c r="AA30" s="51"/>
+      <c r="AB30" s="51"/>
+      <c r="AC30" s="51"/>
+      <c r="AD30" s="51"/>
+      <c r="AE30" s="51"/>
       <c r="AF30" s="3"/>
     </row>
     <row r="31" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2130,96 +2226,96 @@
       <c r="C31" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J31" s="49" t="s">
+      <c r="J31" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="49"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="48"/>
-      <c r="AB31" s="48"/>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="48"/>
-      <c r="AE31" s="48"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
+      <c r="X31" s="51"/>
+      <c r="Y31" s="51"/>
+      <c r="Z31" s="51"/>
+      <c r="AA31" s="51"/>
+      <c r="AB31" s="51"/>
+      <c r="AC31" s="51"/>
+      <c r="AD31" s="51"/>
+      <c r="AE31" s="51"/>
       <c r="AF31" s="3"/>
     </row>
     <row r="32" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="48"/>
-      <c r="AA32" s="48"/>
-      <c r="AB32" s="48"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="48"/>
-      <c r="AE32" s="48"/>
+      <c r="X32" s="51"/>
+      <c r="Y32" s="51"/>
+      <c r="Z32" s="51"/>
+      <c r="AA32" s="51"/>
+      <c r="AB32" s="51"/>
+      <c r="AC32" s="51"/>
+      <c r="AD32" s="51"/>
+      <c r="AE32" s="51"/>
       <c r="AF32" s="3"/>
     </row>
     <row r="33" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="48"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="48"/>
-      <c r="AE33" s="48"/>
+      <c r="X33" s="51"/>
+      <c r="Y33" s="51"/>
+      <c r="Z33" s="51"/>
+      <c r="AA33" s="51"/>
+      <c r="AB33" s="51"/>
+      <c r="AC33" s="51"/>
+      <c r="AD33" s="51"/>
+      <c r="AE33" s="51"/>
       <c r="AF33" s="3"/>
     </row>
     <row r="34" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="17"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
       <c r="AF34" s="3"/>
     </row>
     <row r="35" spans="1:32" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
+      <c r="V35" s="21"/>
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35" s="15"/>
@@ -2233,6 +2329,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:AF3"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="J5:M11"/>
+    <mergeCell ref="N5:V11"/>
     <mergeCell ref="A34:V35"/>
     <mergeCell ref="X27:AE28"/>
     <mergeCell ref="X29:AE33"/>
@@ -2240,11 +2341,6 @@
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="S24:T24"/>
     <mergeCell ref="J31:O31"/>
-    <mergeCell ref="A1:AF3"/>
-    <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="Q28:T28"/>
-    <mergeCell ref="J5:M11"/>
-    <mergeCell ref="N5:V11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2256,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2615F299-DD42-4E31-B208-BF3E7E1ECB2B}">
-  <dimension ref="A1:AF35"/>
+  <dimension ref="A1:AO35"/>
   <sheetFormatPr defaultColWidth="2.33203125" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -2268,185 +2364,185 @@
     <col min="33" max="16384" width="2.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="23"/>
-    </row>
-    <row r="2" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="24"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="26"/>
-    </row>
-    <row r="3" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="26"/>
-    </row>
-    <row r="4" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="24"/>
+    </row>
+    <row r="2" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="27"/>
+    </row>
+    <row r="3" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="26"/>
+      <c r="AB3" s="26"/>
+      <c r="AC3" s="26"/>
+      <c r="AD3" s="26"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="27"/>
+    </row>
+    <row r="4" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="38"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="39"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="41"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="42"/>
       <c r="AF6" s="3"/>
     </row>
-    <row r="7" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="42"/>
       <c r="AF7" s="3"/>
     </row>
-    <row r="8" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="41"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="42"/>
       <c r="AF8" s="3"/>
     </row>
-    <row r="9" spans="1:32" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:41" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2456,19 +2552,19 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="41"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="42"/>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
@@ -2480,7 +2576,7 @@
       <c r="AE9" s="6"/>
       <c r="AF9" s="7"/>
     </row>
-    <row r="10" spans="1:32" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:41" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2490,19 +2586,19 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="41"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="42"/>
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
@@ -2514,7 +2610,7 @@
       <c r="AE10" s="6"/>
       <c r="AF10" s="7"/>
     </row>
-    <row r="11" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:41" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2524,19 +2620,19 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="44"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="45"/>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
@@ -2548,7 +2644,7 @@
       <c r="AE11" s="6"/>
       <c r="AF11" s="7"/>
     </row>
-    <row r="12" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:41" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2563,15 +2659,18 @@
       <c r="L12" s="5"/>
       <c r="AF12" s="9"/>
     </row>
-    <row r="13" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
       <c r="AF13" s="3"/>
-    </row>
-    <row r="14" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AO13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2"/>
       <c r="AF14" s="3"/>
     </row>
-    <row r="15" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="D15" s="12"/>
@@ -2599,7 +2698,7 @@
       <c r="X15" s="12"/>
       <c r="AF15" s="3"/>
     </row>
-    <row r="16" spans="1:32" s="8" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:41" s="8" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="13"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -2681,7 +2780,7 @@
     <row r="19" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13"/>
       <c r="C19" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
@@ -2725,24 +2824,24 @@
     </row>
     <row r="24" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
-      <c r="M24" s="45">
+      <c r="M24" s="46">
         <v>2026</v>
       </c>
-      <c r="N24" s="45"/>
+      <c r="N24" s="46"/>
       <c r="O24" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="P24" s="45">
+      <c r="P24" s="46">
         <v>5</v>
       </c>
-      <c r="Q24" s="45"/>
+      <c r="Q24" s="46"/>
       <c r="R24" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="S24" s="45">
-        <v>12</v>
-      </c>
-      <c r="T24" s="45"/>
+      <c r="S24" s="46">
+        <v>19</v>
+      </c>
+      <c r="T24" s="46"/>
       <c r="U24" s="8" t="s">
         <v>3</v>
       </c>
@@ -2764,22 +2863,22 @@
       <c r="J27" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
       <c r="U27" s="5"/>
       <c r="W27" s="5"/>
-      <c r="X27" s="47" t="s">
+      <c r="X27" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="47"/>
-      <c r="AC27" s="47"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="47"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="50"/>
+      <c r="AA27" s="50"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="50"/>
+      <c r="AE27" s="50"/>
       <c r="AF27" s="9"/>
     </row>
     <row r="28" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -2790,20 +2889,20 @@
       <c r="J28" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
       <c r="U28" s="5"/>
       <c r="W28" s="5"/>
-      <c r="X28" s="47"/>
-      <c r="Y28" s="47"/>
-      <c r="Z28" s="47"/>
-      <c r="AA28" s="47"/>
-      <c r="AB28" s="47"/>
-      <c r="AC28" s="47"/>
-      <c r="AD28" s="47"/>
-      <c r="AE28" s="47"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
+      <c r="AA28" s="50"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="50"/>
+      <c r="AE28" s="50"/>
       <c r="AF28" s="9"/>
     </row>
     <row r="29" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2814,14 +2913,14 @@
       <c r="J29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="48"/>
-      <c r="AE29" s="48"/>
+      <c r="X29" s="51"/>
+      <c r="Y29" s="51"/>
+      <c r="Z29" s="51"/>
+      <c r="AA29" s="51"/>
+      <c r="AB29" s="51"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="51"/>
+      <c r="AE29" s="51"/>
       <c r="AF29" s="3"/>
     </row>
     <row r="30" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2829,14 +2928,14 @@
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="48"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="48"/>
-      <c r="AE30" s="48"/>
+      <c r="X30" s="51"/>
+      <c r="Y30" s="51"/>
+      <c r="Z30" s="51"/>
+      <c r="AA30" s="51"/>
+      <c r="AB30" s="51"/>
+      <c r="AC30" s="51"/>
+      <c r="AD30" s="51"/>
+      <c r="AE30" s="51"/>
       <c r="AF30" s="3"/>
     </row>
     <row r="31" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2844,96 +2943,96 @@
       <c r="C31" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J31" s="49" t="s">
+      <c r="J31" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="49"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="48"/>
-      <c r="AB31" s="48"/>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="48"/>
-      <c r="AE31" s="48"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
+      <c r="X31" s="51"/>
+      <c r="Y31" s="51"/>
+      <c r="Z31" s="51"/>
+      <c r="AA31" s="51"/>
+      <c r="AB31" s="51"/>
+      <c r="AC31" s="51"/>
+      <c r="AD31" s="51"/>
+      <c r="AE31" s="51"/>
       <c r="AF31" s="3"/>
     </row>
     <row r="32" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="48"/>
-      <c r="AA32" s="48"/>
-      <c r="AB32" s="48"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="48"/>
-      <c r="AE32" s="48"/>
+      <c r="X32" s="51"/>
+      <c r="Y32" s="51"/>
+      <c r="Z32" s="51"/>
+      <c r="AA32" s="51"/>
+      <c r="AB32" s="51"/>
+      <c r="AC32" s="51"/>
+      <c r="AD32" s="51"/>
+      <c r="AE32" s="51"/>
       <c r="AF32" s="3"/>
     </row>
     <row r="33" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="48"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="48"/>
-      <c r="AE33" s="48"/>
+      <c r="X33" s="51"/>
+      <c r="Y33" s="51"/>
+      <c r="Z33" s="51"/>
+      <c r="AA33" s="51"/>
+      <c r="AB33" s="51"/>
+      <c r="AC33" s="51"/>
+      <c r="AD33" s="51"/>
+      <c r="AE33" s="51"/>
       <c r="AF33" s="3"/>
     </row>
     <row r="34" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="17"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
       <c r="AF34" s="3"/>
     </row>
     <row r="35" spans="1:32" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
+      <c r="V35" s="21"/>
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35" s="15"/>
@@ -2966,4 +3065,1274 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EE79BE-E9B3-461B-AF8D-5290FE4015C8}">
+  <dimension ref="A1:AO35"/>
+  <sheetFormatPr defaultColWidth="2.33203125" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="2.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="2.33203125" style="1"/>
+    <col min="14" max="16" width="3" style="1" customWidth="1"/>
+    <col min="17" max="29" width="2.33203125" style="1"/>
+    <col min="30" max="31" width="1.33203125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="3.6640625" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="2.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:41" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="24"/>
+    </row>
+    <row r="2" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="25"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="27"/>
+    </row>
+    <row r="3" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="25"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="54"/>
+      <c r="X3" s="54"/>
+      <c r="Y3" s="54"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="54"/>
+      <c r="AC3" s="54"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="54"/>
+      <c r="AF3" s="27"/>
+    </row>
+    <row r="4" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="55"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="55"/>
+      <c r="AC4" s="55"/>
+      <c r="AD4" s="55"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="3"/>
+    </row>
+    <row r="5" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="55"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="55"/>
+      <c r="AC5" s="55"/>
+      <c r="AD5" s="55"/>
+      <c r="AE5" s="55"/>
+      <c r="AF5" s="3"/>
+    </row>
+    <row r="6" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="57"/>
+      <c r="V6" s="42"/>
+      <c r="W6" s="55"/>
+      <c r="X6" s="55"/>
+      <c r="Y6" s="55"/>
+      <c r="Z6" s="55"/>
+      <c r="AA6" s="55"/>
+      <c r="AB6" s="55"/>
+      <c r="AC6" s="55"/>
+      <c r="AD6" s="55"/>
+      <c r="AE6" s="55"/>
+      <c r="AF6" s="3"/>
+    </row>
+    <row r="7" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="57"/>
+      <c r="P7" s="57"/>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="57"/>
+      <c r="T7" s="57"/>
+      <c r="U7" s="57"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="55"/>
+      <c r="X7" s="55"/>
+      <c r="Y7" s="55"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="55"/>
+      <c r="AC7" s="55"/>
+      <c r="AD7" s="55"/>
+      <c r="AE7" s="55"/>
+      <c r="AF7" s="3"/>
+    </row>
+    <row r="8" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="57"/>
+      <c r="V8" s="42"/>
+      <c r="W8" s="55"/>
+      <c r="X8" s="55"/>
+      <c r="Y8" s="55"/>
+      <c r="Z8" s="55"/>
+      <c r="AA8" s="55"/>
+      <c r="AB8" s="55"/>
+      <c r="AC8" s="55"/>
+      <c r="AD8" s="55"/>
+      <c r="AE8" s="55"/>
+      <c r="AF8" s="3"/>
+    </row>
+    <row r="9" spans="1:41" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="4"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="57"/>
+      <c r="P9" s="57"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="57"/>
+      <c r="T9" s="57"/>
+      <c r="U9" s="57"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="59"/>
+      <c r="X9" s="59"/>
+      <c r="Y9" s="59"/>
+      <c r="Z9" s="59"/>
+      <c r="AA9" s="59"/>
+      <c r="AB9" s="59"/>
+      <c r="AC9" s="59"/>
+      <c r="AD9" s="59"/>
+      <c r="AE9" s="59"/>
+      <c r="AF9" s="7"/>
+    </row>
+    <row r="10" spans="1:41" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="57"/>
+      <c r="S10" s="57"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="57"/>
+      <c r="V10" s="42"/>
+      <c r="W10" s="59"/>
+      <c r="X10" s="59"/>
+      <c r="Y10" s="59"/>
+      <c r="Z10" s="59"/>
+      <c r="AA10" s="59"/>
+      <c r="AB10" s="59"/>
+      <c r="AC10" s="59"/>
+      <c r="AD10" s="59"/>
+      <c r="AE10" s="59"/>
+      <c r="AF10" s="7"/>
+    </row>
+    <row r="11" spans="1:41" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="4"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="45"/>
+      <c r="W11" s="59"/>
+      <c r="X11" s="59"/>
+      <c r="Y11" s="59"/>
+      <c r="Z11" s="59"/>
+      <c r="AA11" s="59"/>
+      <c r="AB11" s="59"/>
+      <c r="AC11" s="59"/>
+      <c r="AD11" s="59"/>
+      <c r="AE11" s="59"/>
+      <c r="AF11" s="7"/>
+    </row>
+    <row r="12" spans="1:41" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="60"/>
+      <c r="P12" s="60"/>
+      <c r="Q12" s="60"/>
+      <c r="R12" s="60"/>
+      <c r="S12" s="60"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="60"/>
+      <c r="W12" s="60"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="60"/>
+      <c r="Z12" s="60"/>
+      <c r="AA12" s="60"/>
+      <c r="AB12" s="60"/>
+      <c r="AC12" s="60"/>
+      <c r="AD12" s="60"/>
+      <c r="AE12" s="60"/>
+      <c r="AF12" s="9"/>
+    </row>
+    <row r="13" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="55"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="55"/>
+      <c r="U13" s="55"/>
+      <c r="V13" s="55"/>
+      <c r="W13" s="55"/>
+      <c r="X13" s="55"/>
+      <c r="Y13" s="55"/>
+      <c r="Z13" s="55"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="55"/>
+      <c r="AC13" s="55"/>
+      <c r="AD13" s="55"/>
+      <c r="AE13" s="55"/>
+      <c r="AF13" s="3"/>
+      <c r="AO13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="53"/>
+      <c r="W14" s="53"/>
+      <c r="X14" s="53"/>
+      <c r="Y14" s="53"/>
+      <c r="Z14" s="53"/>
+      <c r="AA14" s="53"/>
+      <c r="AB14" s="53"/>
+      <c r="AC14" s="53"/>
+      <c r="AD14" s="53"/>
+      <c r="AE14" s="53"/>
+      <c r="AF14" s="48"/>
+    </row>
+    <row r="15" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="47"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="53"/>
+      <c r="U15" s="53"/>
+      <c r="V15" s="53"/>
+      <c r="W15" s="53"/>
+      <c r="X15" s="53"/>
+      <c r="Y15" s="53"/>
+      <c r="Z15" s="53"/>
+      <c r="AA15" s="53"/>
+      <c r="AB15" s="53"/>
+      <c r="AC15" s="53"/>
+      <c r="AD15" s="53"/>
+      <c r="AE15" s="53"/>
+      <c r="AF15" s="48"/>
+    </row>
+    <row r="16" spans="1:41" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="13"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="60"/>
+      <c r="P16" s="60"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="60"/>
+      <c r="W16" s="60"/>
+      <c r="X16" s="60"/>
+      <c r="Y16" s="60"/>
+      <c r="Z16" s="60"/>
+      <c r="AA16" s="60"/>
+      <c r="AB16" s="60"/>
+      <c r="AC16" s="60"/>
+      <c r="AD16" s="60"/>
+      <c r="AE16" s="60"/>
+      <c r="AF16" s="9"/>
+    </row>
+    <row r="17" spans="1:32" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="13"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="60"/>
+      <c r="Y17" s="60"/>
+      <c r="Z17" s="60"/>
+      <c r="AA17" s="60"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="60"/>
+      <c r="AD17" s="60"/>
+      <c r="AE17" s="60"/>
+      <c r="AF17" s="9"/>
+    </row>
+    <row r="18" spans="1:32" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="13"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
+      <c r="W18" s="60"/>
+      <c r="X18" s="60"/>
+      <c r="Y18" s="60"/>
+      <c r="Z18" s="60"/>
+      <c r="AA18" s="60"/>
+      <c r="AB18" s="60"/>
+      <c r="AC18" s="60"/>
+      <c r="AD18" s="60"/>
+      <c r="AE18" s="60"/>
+      <c r="AF18" s="9"/>
+    </row>
+    <row r="19" spans="1:32" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="13"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="X19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="60"/>
+      <c r="AA19" s="60"/>
+      <c r="AB19" s="60"/>
+      <c r="AC19" s="60"/>
+      <c r="AD19" s="60"/>
+      <c r="AE19" s="60"/>
+      <c r="AF19" s="9"/>
+    </row>
+    <row r="20" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="55"/>
+      <c r="P20" s="55"/>
+      <c r="Q20" s="55"/>
+      <c r="R20" s="55"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="55"/>
+      <c r="U20" s="55"/>
+      <c r="V20" s="55"/>
+      <c r="W20" s="55"/>
+      <c r="X20" s="55"/>
+      <c r="Y20" s="55"/>
+      <c r="Z20" s="55"/>
+      <c r="AA20" s="55"/>
+      <c r="AB20" s="55"/>
+      <c r="AC20" s="55"/>
+      <c r="AD20" s="55"/>
+      <c r="AE20" s="55"/>
+      <c r="AF20" s="3"/>
+    </row>
+    <row r="21" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="55"/>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55"/>
+      <c r="W21" s="55"/>
+      <c r="X21" s="55"/>
+      <c r="Y21" s="55"/>
+      <c r="Z21" s="55"/>
+      <c r="AA21" s="55"/>
+      <c r="AB21" s="55"/>
+      <c r="AC21" s="55"/>
+      <c r="AD21" s="55"/>
+      <c r="AE21" s="55"/>
+      <c r="AF21" s="3"/>
+    </row>
+    <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="55"/>
+      <c r="P22" s="55"/>
+      <c r="Q22" s="55"/>
+      <c r="R22" s="55"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="55"/>
+      <c r="U22" s="55"/>
+      <c r="V22" s="55"/>
+      <c r="W22" s="55"/>
+      <c r="X22" s="55"/>
+      <c r="Y22" s="55"/>
+      <c r="Z22" s="55"/>
+      <c r="AA22" s="55"/>
+      <c r="AB22" s="55"/>
+      <c r="AC22" s="55"/>
+      <c r="AD22" s="55"/>
+      <c r="AE22" s="55"/>
+      <c r="AF22" s="3"/>
+    </row>
+    <row r="23" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="14"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="60"/>
+      <c r="X23" s="60"/>
+      <c r="Y23" s="60"/>
+      <c r="Z23" s="60"/>
+      <c r="AA23" s="60"/>
+      <c r="AB23" s="60"/>
+      <c r="AC23" s="60"/>
+      <c r="AD23" s="60"/>
+      <c r="AE23" s="60"/>
+      <c r="AF23" s="9"/>
+    </row>
+    <row r="24" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="13"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="64">
+        <v>2026</v>
+      </c>
+      <c r="N24" s="64"/>
+      <c r="O24" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P24" s="64">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="S24" s="64">
+        <v>28</v>
+      </c>
+      <c r="T24" s="64"/>
+      <c r="U24" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AA24" s="60"/>
+      <c r="AB24" s="60"/>
+      <c r="AC24" s="60"/>
+      <c r="AD24" s="60"/>
+      <c r="AE24" s="60"/>
+      <c r="AF24" s="9"/>
+    </row>
+    <row r="25" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="13"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="60"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="60"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="60"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="60"/>
+      <c r="V25" s="60"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="60"/>
+      <c r="Z25" s="60"/>
+      <c r="AA25" s="60"/>
+      <c r="AB25" s="60"/>
+      <c r="AC25" s="60"/>
+      <c r="AD25" s="60"/>
+      <c r="AE25" s="60"/>
+      <c r="AF25" s="9"/>
+    </row>
+    <row r="26" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="13"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="60"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="60"/>
+      <c r="S26" s="60"/>
+      <c r="T26" s="60"/>
+      <c r="U26" s="60"/>
+      <c r="V26" s="60"/>
+      <c r="W26" s="60"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="60"/>
+      <c r="AA26" s="60"/>
+      <c r="AB26" s="60"/>
+      <c r="AC26" s="60"/>
+      <c r="AD26" s="60"/>
+      <c r="AE26" s="60"/>
+      <c r="AF26" s="9"/>
+    </row>
+    <row r="27" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="13"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
+      <c r="M27" s="60"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="65"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="65"/>
+      <c r="T27" s="65"/>
+      <c r="U27" s="58"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="58"/>
+      <c r="X27" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="50"/>
+      <c r="AA27" s="50"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="50"/>
+      <c r="AE27" s="50"/>
+      <c r="AF27" s="9"/>
+    </row>
+    <row r="28" spans="1:32" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="13"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="60"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="65"/>
+      <c r="T28" s="65"/>
+      <c r="U28" s="58"/>
+      <c r="V28" s="60"/>
+      <c r="W28" s="58"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
+      <c r="AA28" s="50"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="50"/>
+      <c r="AE28" s="50"/>
+      <c r="AF28" s="9"/>
+    </row>
+    <row r="29" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="55"/>
+      <c r="C29" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="55"/>
+      <c r="Q29" s="55"/>
+      <c r="R29" s="55"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="55"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="55"/>
+      <c r="X29" s="51"/>
+      <c r="Y29" s="51"/>
+      <c r="Z29" s="51"/>
+      <c r="AA29" s="51"/>
+      <c r="AB29" s="51"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="51"/>
+      <c r="AE29" s="51"/>
+      <c r="AF29" s="3"/>
+    </row>
+    <row r="30" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="55"/>
+      <c r="Q30" s="55"/>
+      <c r="R30" s="55"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="55"/>
+      <c r="U30" s="55"/>
+      <c r="V30" s="55"/>
+      <c r="W30" s="55"/>
+      <c r="X30" s="51"/>
+      <c r="Y30" s="51"/>
+      <c r="Z30" s="51"/>
+      <c r="AA30" s="51"/>
+      <c r="AB30" s="51"/>
+      <c r="AC30" s="51"/>
+      <c r="AD30" s="51"/>
+      <c r="AE30" s="51"/>
+      <c r="AF30" s="3"/>
+    </row>
+    <row r="31" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="55"/>
+      <c r="C31" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="55"/>
+      <c r="R31" s="55"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="55"/>
+      <c r="V31" s="55"/>
+      <c r="W31" s="55"/>
+      <c r="X31" s="51"/>
+      <c r="Y31" s="51"/>
+      <c r="Z31" s="51"/>
+      <c r="AA31" s="51"/>
+      <c r="AB31" s="51"/>
+      <c r="AC31" s="51"/>
+      <c r="AD31" s="51"/>
+      <c r="AE31" s="51"/>
+      <c r="AF31" s="3"/>
+    </row>
+    <row r="32" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="55"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="55"/>
+      <c r="U32" s="55"/>
+      <c r="V32" s="55"/>
+      <c r="W32" s="55"/>
+      <c r="X32" s="51"/>
+      <c r="Y32" s="51"/>
+      <c r="Z32" s="51"/>
+      <c r="AA32" s="51"/>
+      <c r="AB32" s="51"/>
+      <c r="AC32" s="51"/>
+      <c r="AD32" s="51"/>
+      <c r="AE32" s="51"/>
+      <c r="AF32" s="3"/>
+    </row>
+    <row r="33" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="55"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="55"/>
+      <c r="U33" s="55"/>
+      <c r="V33" s="55"/>
+      <c r="W33" s="55"/>
+      <c r="X33" s="51"/>
+      <c r="Y33" s="51"/>
+      <c r="Z33" s="51"/>
+      <c r="AA33" s="51"/>
+      <c r="AB33" s="51"/>
+      <c r="AC33" s="51"/>
+      <c r="AD33" s="51"/>
+      <c r="AE33" s="51"/>
+      <c r="AF33" s="3"/>
+    </row>
+    <row r="34" spans="1:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="18"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
+      <c r="K34" s="67"/>
+      <c r="L34" s="67"/>
+      <c r="M34" s="67"/>
+      <c r="N34" s="67"/>
+      <c r="O34" s="67"/>
+      <c r="P34" s="67"/>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="67"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="67"/>
+      <c r="U34" s="67"/>
+      <c r="V34" s="67"/>
+      <c r="W34" s="55"/>
+      <c r="X34" s="55"/>
+      <c r="Y34" s="55"/>
+      <c r="Z34" s="55"/>
+      <c r="AA34" s="55"/>
+      <c r="AB34" s="55"/>
+      <c r="AC34" s="55"/>
+      <c r="AD34" s="55"/>
+      <c r="AE34" s="55"/>
+      <c r="AF34" s="3"/>
+    </row>
+    <row r="35" spans="1:32" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="20"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
+      <c r="V35" s="21"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
+      <c r="Z35" s="15"/>
+      <c r="AA35" s="15"/>
+      <c r="AB35" s="15"/>
+      <c r="AC35" s="15"/>
+      <c r="AD35" s="15"/>
+      <c r="AE35" s="15"/>
+      <c r="AF35" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A34:V35"/>
+    <mergeCell ref="A1:AF3"/>
+    <mergeCell ref="J5:M11"/>
+    <mergeCell ref="N5:V11"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="A14:AF15"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="X27:AE28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="X29:AE33"/>
+    <mergeCell ref="J31:O31"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C19:E19"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.51181102362204722" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>